--- a/deliverables/pm/excel_templates/03_store_listings_v1.0.xlsx
+++ b/deliverables/pm/excel_templates/03_store_listings_v1.0.xlsx
@@ -8,16 +8,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入模板" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="正确样例" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误样例" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="枚举值" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_meta" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入模板" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="正确样例" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误样例" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="枚举值" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'导入模板'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'正确样例'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'错误样例'!$A$1:$M$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'枚举值'!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导入模板'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'正确样例'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'错误样例'!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'枚举值'!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -616,6 +617,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>schemaIdentifier</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>jiugeng.amazon.erp.import</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>importType</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>STORE_LISTINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>templateVersion</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>maxDataRows</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -713,7 +774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1112,7 +1173,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1433,7 +1494,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/deliverables/pm/excel_templates/03_store_listings_v1.0.xlsx
+++ b/deliverables/pm/excel_templates/03_store_listings_v1.0.xlsx
@@ -1179,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1485,6 +1485,254 @@
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>FBM 不得填写 FNSKU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TEST-STORE-03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ATVPDKIKX0DER</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>BAD-DUP-FNSKU</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>B0BADF0002</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>STANDALONE</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>TEST-P001</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>TEST-SKU001</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>X00TEST003</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>同店非空 FNSKU 与正确样例重复</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TEST-STORE-02</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>ATVPDKIKX0DER</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>BAD-DUP-ACTIVE</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>B0BADA0001</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>STANDALONE</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>TEST-P001</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>TEST-SKU001</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>同一 SKU 在同店已有 ACTIVE Listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TEST-STORE-02</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ATVPDKIKX0DER</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>BAD-CROSS-PARENT</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>B0BADC0002</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>TEST-P001</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>TEST-SKU002</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>TEST-PARENT-01</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>ColorSize</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>X00BAD0002</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>子体引用其他店铺的父体</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TEST-STORE-01</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>ATVPDKIKX0DER</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>BAD-THEME</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>B0BADT0001</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>TEST-P001</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>TEST-SKU002</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>TEST-PARENT-01</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>X00BAD0003</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>父子 variation_theme 不一致</t>
         </is>
       </c>
     </row>
